--- a/output/full_scan/batch_seq2_2026-09-24.xlsx
+++ b/output/full_scan/batch_seq2_2026-09-24.xlsx
@@ -555,7 +555,7 @@
         <v>83.25558216848839</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>39.15352497227123</v>
+        <v>39.1535250548378</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>3.57826186362103</v>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>61.52360682666525</v>
+        <v>61.52360685553324</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>21.45829352083146</v>
+        <v>21.45829360465729</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>1.399461610896603</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.0543039153429717</v>
+        <v>0.0543039153326651</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>73.43956867615418</v>
+        <v>73.43956865220102</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>23.04718026547836</v>
+        <v>23.04718026547837</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>1.697784647064377</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>28.30698037244533</v>
+        <v>28.30698037306346</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>63.40460256136876</v>
+        <v>63.40460261947977</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>12.86431561291544</v>
+        <v>12.86431566409688</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>3.328322721335401</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>70.68209005492903</v>
+        <v>70.68209008270458</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>18.21250768145965</v>
+        <v>18.21250769756018</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>7.26952738371643</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1149232343980671</v>
+        <v>0.1149232343774629</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>66.72094490568611</v>
+        <v>66.7209448848851</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15.65026103222633</v>
+        <v>15.65026104863387</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>1.599201317282816</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.846212663405184</v>
+        <v>1.846212663425788</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>63.13986796177769</v>
+        <v>63.13986796031234</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>31.21474088535007</v>
+        <v>31.21474093397769</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>0.911490441868601</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.9438311515411986</v>
+        <v>0.9438311526745444</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>62.78756123689922</v>
+        <v>62.78756111578539</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>17.33466613560573</v>
+        <v>17.33466616850555</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>2.567937412073894</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.01216985626756</v>
+        <v>0.0121698563087709</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>71.40047749470253</v>
+        <v>71.40047750220673</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>20.80625716752162</v>
+        <v>20.8062571865306</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>8.669364832503575</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.9139053916972122</v>
+        <v>0.9139053916869092</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>72.31279042776772</v>
+        <v>72.31279044033816</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>31.73969109759653</v>
+        <v>31.73969102494073</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>5.425980696454842</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>2.084524790288681</v>
+        <v>2.084524790216566</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>71.48097168907225</v>
+        <v>71.48097170333745</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>13.37329662986686</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.7738026823945749</v>
+        <v>0.7738026823636652</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>80.0023158368968</v>
+        <v>80.00231580241359</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>33.24858792086</v>
+        <v>33.24858791721046</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>4.339920615022826</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.1781430735214165</v>
+        <v>0.1781430735111142</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>69.73596779201912</v>
+        <v>69.73596790114054</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>24.4992961237239</v>
+        <v>24.49929608283283</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>1.821595405969461</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>1.419079159061001</v>
+        <v>1.419079158525254</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>65.60795457715669</v>
+        <v>65.60795457427821</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>29.78723514507839</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.4125170851102486</v>
+        <v>0.4125170851514728</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>72.26910617590815</v>
+        <v>72.26910615448926</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>38.41753897507133</v>
+        <v>38.41753898301345</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>0.5258153072103766</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.4903598884448339</v>
+        <v>0.4903598887539309</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>60.27820053113104</v>
+        <v>60.27820053529262</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>11.88084300930299</v>
+        <v>11.88084293819636</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>2.316271965131233</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.3660201430255875</v>
+        <v>0.3660201430770984</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>66.36130388869849</v>
+        <v>66.36130403400838</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>16.59283375677133</v>
+        <v>16.59283375677134</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>2.586718611225685</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.0510474651491385</v>
+        <v>0.0510474650770185</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>60.5790191541663</v>
+        <v>60.57901915967555</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>14.55358711018699</v>
+        <v>14.5535870403229</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>3.025799183202606</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.2333930133098233</v>
+        <v>0.2333930133304308</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>61.4533908289478</v>
+        <v>61.45339083019682</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>20.15037995846434</v>
+        <v>20.15037993298096</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>1.422514985430364</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.3172797711423991</v>
+        <v>0.3172797712866504</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>866.2488403081832</v>
+        <v>866.2488403081827</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>2295</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>56.50475379166264</v>
+        <v>56.50475377720559</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>21.20109977090515</v>
+        <v>21.20109969236486</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>0.8756089640920937</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>21.10161428724874</v>
+        <v>21.10161429157612</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>808.4971567745301</v>
+        <v>808.4971567745307</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>94.5</v>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>67.71520575645481</v>
+        <v>67.71520577577243</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>18.98851964617666</v>
+        <v>18.98851966838041</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>0.7709940901375543</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.6676947246579903</v>
+        <v>0.6676947246991919</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>793.2082350297167</v>
+        <v>793.2082350297164</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>154</v>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>62.38473273670472</v>
+        <v>62.3847327371945</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>27.02854602622155</v>
+        <v>27.02854600078537</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>0.7889216797135905</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>1.875098415986466</v>
+        <v>1.875098416017385</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>62.23505885160986</v>
+        <v>62.23505883308314</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>15.04889234516742</v>
+        <v>15.04889246401966</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>4.216173408695211</v>
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.0514208431337379</v>
+        <v>0.0514208430925262</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>68.13812007099087</v>
+        <v>68.13812009391965</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>50.31224695304909</v>
+        <v>50.31224695337114</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>1.231263242640805</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.1797863891834445</v>
+        <v>0.1797863891216249</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>777.8397526457042</v>
+        <v>777.8397526457039</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>1910</v>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>61.09704685651185</v>
+        <v>61.09704688862043</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>14.74363392315211</v>
+        <v>14.74363391140123</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>0.7535591432985408</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>24.26057399252807</v>
+        <v>24.26057399355846</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>65.91778411112352</v>
+        <v>65.91778410949308</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>32.71343465516438</v>
+        <v>32.71343472074192</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>1.222829457576021</v>
@@ -1895,7 +1895,7 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.6009471284430428</v>
+        <v>0.6009471284636514</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>77.98182272195031</v>
+        <v>77.98182271968813</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>21.24047694833577</v>
+        <v>21.24047694351013</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>3.8189125292083</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1.139684637167206</v>
+        <v>1.13968463721872</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1983,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>61.29276921662658</v>
+        <v>61.29276912310355</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>28.68496941006253</v>
+        <v>28.68496938646548</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>1.982987589937785</v>
@@ -2001,7 +2001,7 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.6090793911819152</v>
+        <v>0.6090793914291825</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>78.23134097404534</v>
+        <v>78.23134097693885</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>54.73031821071515</v>
+        <v>54.73031823405492</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>1.281871875677614</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.8578590457483029</v>
+        <v>0.8578590457689073</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2089,10 +2089,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>56.16571209358216</v>
+        <v>56.1657121651676</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>16.65012829587331</v>
+        <v>16.65012841317388</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>0.9982294208623154</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>5.88294320702941</v>
+        <v>5.882943205999165</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2142,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>61.14083303163455</v>
+        <v>61.14083303068553</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>46.45998939184315</v>
+        <v>46.45998933904724</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>1.846920244307975</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.759658374310531</v>
+        <v>0.7596583743414378</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>56.9781086987737</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>22.89387244559182</v>
+        <v>22.89387243280152</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>0.4884098637128295</v>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>52.49959945499708</v>
+        <v>52.49959955127451</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>13.12121206082884</v>
+        <v>13.12121206146299</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>0.8735916450426024</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>7.172786220848144</v>
+        <v>7.172786219435558</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>696.5828271637669</v>
+        <v>696.582827163767</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>1105</v>
@@ -2301,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>55.24086950584739</v>
+        <v>55.2408695327356</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>17.47061855391829</v>
+        <v>17.47061859219871</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>1.707497733670249</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>4.706526870306053</v>
+        <v>4.706526867009289</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>53.04866485304681</v>
+        <v>53.04866488502824</v>
       </c>
       <c r="I36" s="2" t="n">
         <v>20.38094121461072</v>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>58.45399712206655</v>
+        <v>58.45399714809518</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>17.3486314097165</v>
+        <v>17.3486314214843</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>1.178077043108767</v>
@@ -2460,10 +2460,10 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>59.44031540114831</v>
+        <v>59.44031563177893</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>25.67092103755829</v>
+        <v>25.67092103926446</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>0.4909002749187948</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>58.15589189769091</v>
+        <v>58.15589195654061</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>28.5546418947065</v>
+        <v>28.55464188432888</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>0.335888296987395</v>
@@ -2531,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.2001268423439213</v>
+        <v>0.2001268423542321</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>668.6221919298723</v>
+        <v>668.6221919298697</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>24.2</v>
@@ -2566,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>62.86701346467799</v>
+        <v>62.86701347114266</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>28.3749367993879</v>
+        <v>28.37493677616176</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>0.7066710767768115</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.2441681919207046</v>
+        <v>0.2441681919310072</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>67.24610336057306</v>
+        <v>67.24610331782404</v>
       </c>
       <c r="I41" s="2" t="n">
         <v>37.0978979786032</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>56.88032470617075</v>
+        <v>56.88032474286079</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>16.0945192984965</v>
+        <v>16.09451932354369</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>0.6618423597241979</v>
@@ -2690,7 +2690,7 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>5.806812290206052</v>
+        <v>5.806812289175381</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2725,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>57.8806218164573</v>
+        <v>57.88062168546158</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>18.24167902877317</v>
+        <v>18.2416790690936</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>0.8344986695615418</v>
@@ -2743,7 +2743,7 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.0468648396905431</v>
+        <v>-0.046864839546301</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>55.66447729616792</v>
+        <v>55.66447730638476</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>26.99262310125025</v>
+        <v>26.99262304760306</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>0.3327969981423154</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.0149948460559462</v>
+        <v>0.0149948460353415</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>53.78857555350238</v>
+        <v>53.78857552995055</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>11.99139763989286</v>
+        <v>11.99139762338204</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>0.6299407334010502</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.0186165254324392</v>
+        <v>0.0186165255972894</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>64.09792672316897</v>
+        <v>64.09792680708642</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>24.64820788468675</v>
+        <v>24.64820786565915</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>0.8816440495666996</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>1.06868752623746</v>
+        <v>1.06868752603141</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2937,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>40.19989748879404</v>
+        <v>40.1998975181052</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>20.31204084536891</v>
+        <v>20.3120408453689</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0.348709778448881</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.2893096629740911</v>
+        <v>-0.2893096629431889</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>50.99230227256598</v>
+        <v>50.99230228361736</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>20.19452048203599</v>
+        <v>20.1945205315538</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>0.6928648506534498</v>
@@ -3008,7 +3008,7 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.2945693404601481</v>
+        <v>0.2945693411813457</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3043,10 +3043,10 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>51.06394686910231</v>
+        <v>51.06394682450708</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>17.65173618529858</v>
+        <v>17.6517361680875</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>0.8066617408883685</v>
@@ -3061,7 +3061,7 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.2067257960884657</v>
+        <v>-0.206725796006041</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>611.8211926030069</v>
+        <v>611.821192603007</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>50.2</v>
@@ -3096,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>57.43132751933754</v>
+        <v>57.43132751032911</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45.14199078369564</v>
+        <v>45.14199076074179</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>0.4681960387412687</v>
@@ -3114,7 +3114,7 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.4053591356170094</v>
+        <v>0.4053591356891382</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>50.20592838025482</v>
+        <v>50.20592835776312</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>31.51267905176863</v>
+        <v>31.51267905561445</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>0.4091265424535423</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-1.89697271895183</v>
+        <v>-1.896972718848794</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3202,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>53.66341766691446</v>
+        <v>53.66341776137234</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>29.54057738201457</v>
+        <v>29.54057737072786</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>0.4255381368334286</v>
@@ -3241,7 +3241,7 @@
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>601.6502080181848</v>
+        <v>601.6502080181847</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>124</v>
@@ -3255,10 +3255,10 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>56.93159659403687</v>
+        <v>56.93159660267919</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>16.38853727730437</v>
+        <v>16.38853724915111</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>0.6563858128763391</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>1.354916534789028</v>
+        <v>1.354916534809625</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>56.19444628818052</v>
+        <v>56.1944462516282</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>23.42866125957441</v>
+        <v>23.4286612363266</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>0.8317861121425919</v>
@@ -3347,7 +3347,7 @@
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>592.684280132823</v>
+        <v>592.6842801328227</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>167</v>
@@ -3361,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>56.36437439595669</v>
+        <v>56.36437449652539</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>16.98581197164371</v>
+        <v>16.98581197791972</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>0.3693269264607346</v>
@@ -3379,7 +3379,7 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.867345159183964</v>
+        <v>-0.8673451593900072</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3414,10 +3414,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>59.451294900279</v>
+        <v>59.4512949261993</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>29.55860848466817</v>
+        <v>29.55860870134153</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>2.201451231272236</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.08809377654989541</v>
+        <v>0.0880937765086828</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>53.87496281565777</v>
+        <v>53.87496282362075</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>28.12096989794366</v>
+        <v>28.12096986168024</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>0.6942681600017268</v>
@@ -3520,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>58.03948122829384</v>
+        <v>58.0394812266694</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>39.23138546861696</v>
+        <v>39.231385455683</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>0.2517450244329172</v>
@@ -3538,7 +3538,7 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.2991476718771848</v>
+        <v>0.2991476719080945</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>53.89910723354853</v>
+        <v>53.89910724804796</v>
       </c>
       <c r="I59" s="2" t="n">
         <v>19.18509190774027</v>
@@ -3626,7 +3626,7 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>49.63413591332306</v>
+        <v>49.63413642294675</v>
       </c>
       <c r="I60" s="2" t="n">
         <v>21.40773067058689</v>
@@ -3644,7 +3644,7 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.0501257323219804</v>
+        <v>0.0501257319716811</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>54.6495977137179</v>
+        <v>54.64959757484591</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>27.54805265859408</v>
+        <v>27.54805267615896</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>3.476784031269073</v>
@@ -3697,7 +3697,7 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.0257841615301225</v>
+        <v>0.0257841615404256</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3732,10 +3732,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>47.81893155574269</v>
+        <v>47.81893154954295</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>29.57893323724364</v>
+        <v>29.57893331486545</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>0.822446880628226</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>55.22015616145922</v>
+        <v>55.2201563081405</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>26.33068835321714</v>
+        <v>26.33068873153488</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>0.4611256140319837</v>
@@ -3803,7 +3803,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.09536987976233111</v>
+        <v>0.09536988001990269</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>54.7820408244234</v>
+        <v>54.78204090181674</v>
       </c>
       <c r="I64" s="2" t="n">
         <v>12.97180301786524</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>1.117996130915231</v>
+        <v>1.117996130194034</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>558.8202724254422</v>
+        <v>558.8202724254421</v>
       </c>
       <c r="E65" s="2" t="n">
         <v>16.9</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>52.33024767102361</v>
+        <v>52.33024773916122</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>12.57694413462598</v>
+        <v>12.57694436427963</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>2.208413046344201</v>
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.020150735232608</v>
+        <v>0.0201507352016992</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>553.9899795395792</v>
+        <v>553.9899795395779</v>
       </c>
       <c r="E66" s="2" t="n">
         <v>1210</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>31.95493883884777</v>
+        <v>31.95493890474266</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>27.19797756939955</v>
+        <v>27.19797757952495</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>1.574378095044848</v>
@@ -3962,7 +3962,7 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-7.594995947881479</v>
+        <v>-7.594995950972311</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -3997,10 +3997,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>51.74005898462713</v>
+        <v>51.74005904064168</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>9.882345080620729</v>
+        <v>9.882345014757036</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>0.5386985446852695</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.023064077959275</v>
+        <v>-0.0230640779695749</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4050,10 +4050,10 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>51.63203816589986</v>
+        <v>51.63203829532741</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>9.432906713480902</v>
+        <v>9.432906719877687</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>0.7159868276905778</v>
@@ -4068,7 +4068,7 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.0464252807113823</v>
+        <v>-0.0464252815356172</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>55.04428535138489</v>
+        <v>55.04428513067835</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>28.35650975797616</v>
+        <v>28.35650990225773</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>0.7177665360044359</v>
@@ -4121,7 +4121,7 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.046337073873697</v>
+        <v>0.0463370743167217</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4156,10 +4156,10 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>48.53751653256348</v>
+        <v>48.53751656191755</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>21.91575847485553</v>
+        <v>21.91575852228732</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>0.8656377198133017</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-155.0888834110373</v>
+        <v>-155.0888834192808</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4209,10 +4209,10 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>59.69396258170639</v>
+        <v>59.6939625781396</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>37.83834189171453</v>
+        <v>37.83834192865034</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>0.3531446692793465</v>
@@ -4227,7 +4227,7 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.1926529109689052</v>
+        <v>0.1926529109895133</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>52.35737210944555</v>
+        <v>52.35737214724146</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>43.45536529665472</v>
+        <v>43.45536546022988</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>0.4963929529522013</v>
@@ -4301,7 +4301,7 @@
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>520.6381284016575</v>
+        <v>520.6381284016577</v>
       </c>
       <c r="E73" s="2" t="n">
         <v>32.1</v>
@@ -4315,10 +4315,10 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>57.99053255503902</v>
+        <v>57.99053247751765</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>26.58514027354701</v>
+        <v>26.58514037888085</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>0.7999231094171979</v>
@@ -4333,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.1440849565782863</v>
+        <v>0.1440849566710145</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>63.43753461886404</v>
+        <v>63.43753460981142</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>30.67405982817736</v>
+        <v>30.67405982145334</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>0.8241133684576546</v>
@@ -4407,7 +4407,7 @@
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>503.1858370413333</v>
+        <v>503.1858370413334</v>
       </c>
       <c r="E75" s="2" t="n">
         <v>18.1</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>60.38156627315377</v>
+        <v>60.38156630877798</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>26.10436616777936</v>
+        <v>26.10436620170971</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>0.1143523542655371</v>
@@ -4439,7 +4439,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0684869540760412</v>
+        <v>0.0684869540657371</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4474,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>52.68636395309769</v>
+        <v>52.68636399546636</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>53.23323049694837</v>
+        <v>53.23323050810691</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>0.3048147393167196</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0797380867407689</v>
+        <v>-0.0797380867510719</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4527,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>62.95077756466083</v>
+        <v>62.95077757407136</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>18.42382371282245</v>
+        <v>18.42382372875164</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>0.9137849171910698</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>55.10475221952311</v>
+        <v>55.1047521783963</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>15.70724390713507</v>
+        <v>15.70724393783225</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>0.9497727413236708</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.0030477613234057</v>
+        <v>0.0030477613440115</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>493.6177075484915</v>
+        <v>493.6177075484914</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>96.90000000000001</v>
@@ -4633,10 +4633,10 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>54.60088128725902</v>
+        <v>54.60088128528034</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>29.0902073559818</v>
+        <v>29.09020733447712</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>0.5857983676329105</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-1.193539146748313</v>
+        <v>-1.193539146696803</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>492.7186206454234</v>
+        <v>492.7186206454233</v>
       </c>
       <c r="E80" s="2" t="n">
         <v>5050</v>
@@ -4686,10 +4686,10 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>44.92067011307617</v>
+        <v>44.92067012329037</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>14.80333003646863</v>
+        <v>14.80333009481419</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>1.14122775747926</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-36.69661959604674</v>
+        <v>-36.6966195981076</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>42.80882911709481</v>
+        <v>42.80882912318904</v>
       </c>
       <c r="I81" s="2" t="n">
         <v>29.39950428232444</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>2.03780267773231</v>
+        <v>2.037802677526237</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>54.61375001115687</v>
+        <v>54.61375011666983</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>13.00857666753406</v>
+        <v>13.00857678805169</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>0.4739694349534739</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.2179168986296957</v>
+        <v>0.21791689883576</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4845,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>39.48369350767961</v>
+        <v>39.48369348713904</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>20.72426950692124</v>
+        <v>20.72426956059168</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>0.659294730070105</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.3143289563420091</v>
+        <v>-0.3143289562007491</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>47.39581220444071</v>
+        <v>47.39581213383774</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>29.44991742709831</v>
+        <v>29.44991760372634</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>0.6953349428641492</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.3222488189458785</v>
+        <v>0.3222488192549563</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>471.9131822530253</v>
+        <v>471.9131822530221</v>
       </c>
       <c r="E85" s="2" t="n">
         <v>44.4</v>
@@ -4951,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>55.43142488827734</v>
+        <v>55.43142498812896</v>
       </c>
       <c r="I85" s="2" t="n">
         <v>15.04405716390509</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.3312938707118353</v>
+        <v>0.3312938706294127</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>462.9799119548334</v>
+        <v>462.9799119548336</v>
       </c>
       <c r="E86" s="2" t="n">
         <v>1895</v>
@@ -5004,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>42.56844290701254</v>
+        <v>42.56844292585872</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>19.34754076809628</v>
+        <v>19.34754074686855</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>0.7074406009953742</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>3.662632703849738</v>
+        <v>3.662632704055781</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>39.33347978368423</v>
+        <v>39.33347983837968</v>
       </c>
       <c r="I87" s="2" t="n">
         <v>26.8883657037908</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.3327942129299326</v>
+        <v>0.3327942128268994</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>453.8985888713041</v>
+        <v>453.8985888713035</v>
       </c>
       <c r="E88" s="2" t="n">
         <v>19.4</v>
@@ -5110,10 +5110,10 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>55.32579662293614</v>
+        <v>55.32579654607532</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>22.05186254563832</v>
+        <v>22.05186255692423</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>0.7558225980049488</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0742220764127748</v>
+        <v>0.0742220764642882</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>447.4667127234043</v>
+        <v>447.4667127234044</v>
       </c>
       <c r="E89" s="2" t="n">
         <v>63.4</v>
@@ -5163,10 +5163,10 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>48.46569371168716</v>
+        <v>48.46569370567156</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>11.08529073667873</v>
+        <v>11.08529071012327</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>1.300608595932826</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0349018035938122</v>
+        <v>0.0349018034495698</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>54.66097985138877</v>
+        <v>54.66097980135568</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>26.87481328002783</v>
+        <v>26.87481327581776</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>0.6202075356997018</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0283285405169803</v>
+        <v>0.0283285405478894</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>56.37527109926305</v>
+        <v>56.37527100232828</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>26.71613130798281</v>
+        <v>26.71613133297487</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>0.5236319123987626</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.047790384423093</v>
+        <v>0.0477903844437005</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>42.50155320923641</v>
+        <v>42.50155330974846</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>22.20411531493849</v>
+        <v>22.20411526618346</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>0.1993209185384439</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0101202395369079</v>
+        <v>0.0101202395060002</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>24.03494533170769</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>38.86866320666086</v>
+        <v>38.86892600244719</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>4.024376545896833</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.098729714814145</v>
+        <v>0.0987298204493902</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>435.0610665187911</v>
+        <v>435.0610665187907</v>
       </c>
       <c r="E94" s="2" t="n">
         <v>39.15</v>
@@ -5428,10 +5428,10 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>47.62274018410753</v>
+        <v>47.62274014903413</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>22.63269151445136</v>
+        <v>22.63269151558885</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>0.4548821519677418</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.0622745405356318</v>
+        <v>-0.0622745405047166</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>49.94539016837665</v>
+        <v>49.94539023623148</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>12.45688383272324</v>
+        <v>12.45688390542903</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>0.7407744247118293</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>48.37106891888782</v>
+        <v>48.37106893751282</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>9.719419529045666</v>
+        <v>9.719419556413923</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>0.2905782265316657</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.3419494022519285</v>
+        <v>-0.3419494022313389</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>425.06677217245</v>
+        <v>425.0667721724503</v>
       </c>
       <c r="E97" s="2" t="n">
         <v>503</v>
@@ -5587,10 +5587,10 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>50.98652262002247</v>
+        <v>50.9865226241161</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>13.35158289806149</v>
+        <v>13.35158291235801</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>0.6214390799489438</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-1.799493996781589</v>
+        <v>-1.799493996925834</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>424.3920778015263</v>
+        <v>424.3920778015265</v>
       </c>
       <c r="E98" s="2" t="n">
         <v>31.25</v>
@@ -5640,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>50.39573472612715</v>
+        <v>50.39573474178192</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>16.88014083532256</v>
+        <v>16.88014087172363</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>0.5273223571435459</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.2967965957772628</v>
+        <v>0.2967965957566598</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>50.65241520834589</v>
+        <v>50.65241528084524</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>18.77315269045754</v>
+        <v>18.77315272926682</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>0.4997094857052206</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0625257241589052</v>
+        <v>0.06252572422430371</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5746,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>45.53810176893402</v>
+        <v>45.53810219954357</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>20.87364005748489</v>
+        <v>20.87364011162714</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>0.7443935630658249</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.0689249244410654</v>
+        <v>0.0689249244719748</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5799,10 +5799,10 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>42.6110714888149</v>
+        <v>42.61107145159022</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>17.20017052252017</v>
+        <v>17.20017053387249</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>0.9921365922645397</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-2.719742334950148</v>
+        <v>-2.719742333919827</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>416.0662066598725</v>
+        <v>416.0662066598731</v>
       </c>
       <c r="E102" s="2" t="n">
         <v>160.5</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>51.75805820613856</v>
+        <v>51.75805821493263</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>9.466130835368574</v>
+        <v>9.466130890493339</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>0.3492985120162575</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.5100536859770586</v>
+        <v>0.5100536854619164</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5905,10 +5905,10 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>43.83427482779715</v>
+        <v>43.83427481869754</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>10.66383414040512</v>
+        <v>10.66383414540095</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>0.1634282786264011</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-1.441246387401196</v>
+        <v>-1.441246387277534</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>415.8538511576818</v>
+        <v>415.8538511576821</v>
       </c>
       <c r="E104" s="2" t="n">
         <v>164.5</v>
@@ -5958,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>54.79363422911672</v>
+        <v>54.79363426750984</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>18.23809025964745</v>
+        <v>18.23809030224721</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>0.5515459178617894</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.4440739969461661</v>
+        <v>0.4440739966371009</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>414.5696690205949</v>
+        <v>414.5696690205944</v>
       </c>
       <c r="E105" s="2" t="n">
         <v>72</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>50.30766343849118</v>
+        <v>50.30766330252544</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>21.5352465799074</v>
+        <v>21.53524669983813</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>0.5675133672262171</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.2226490267209145</v>
+        <v>0.2226490270918155</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>413.0472715020032</v>
+        <v>413.0472715020033</v>
       </c>
       <c r="E106" s="2" t="n">
         <v>30.5</v>
@@ -6064,10 +6064,10 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>46.97250919464493</v>
+        <v>46.97250901245397</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>47.56281008526805</v>
+        <v>47.56280997490207</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>0.947919825962579</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0266245370752105</v>
+        <v>-0.0266245369824836</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>408.8020832036856</v>
+        <v>408.8020832036853</v>
       </c>
       <c r="E107" s="2" t="n">
         <v>41.7</v>
@@ -6117,7 +6117,7 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>47.35975898273567</v>
+        <v>47.35975898680383</v>
       </c>
       <c r="I107" s="2" t="n">
         <v>15.96400920055124</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>46.99691845428512</v>
+        <v>46.99691849021912</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>22.78955149799961</v>
+        <v>22.78955152617823</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>0.3654301696843968</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0071881533180744</v>
+        <v>0.0071881533139542</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>402.1155659584958</v>
+        <v>402.115565958496</v>
       </c>
       <c r="E109" s="2" t="n">
         <v>33</v>
@@ -6223,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>55.04356229293749</v>
+        <v>55.04356218496165</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>15.18648790643032</v>
+        <v>15.18648798226164</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>0.5754816783205886</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0834548077436733</v>
+        <v>0.08345480779518751</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>393.4660118779009</v>
+        <v>393.4660118778948</v>
       </c>
       <c r="E110" s="2" t="n">
         <v>47</v>
@@ -6276,10 +6276,10 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>54.51055032196647</v>
+        <v>54.51055038557323</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>14.07048697302422</v>
+        <v>14.07048699733008</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>0.4858354331653284</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.1276499161937617</v>
+        <v>0.1276499161525494</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>33.24862680552947</v>
+        <v>33.24862684462182</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>26.98929468279685</v>
+        <v>26.98929462955581</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>1.206476086469957</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.6001838293134414</v>
+        <v>-0.6001838292928241</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>391.2250836811467</v>
+        <v>391.2250836811468</v>
       </c>
       <c r="E112" s="2" t="n">
         <v>41.7</v>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>47.90514288050764</v>
+        <v>47.90514290995312</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>16.52892833033481</v>
+        <v>16.52892838267382</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>0.8102352256506605</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0504651857070094</v>
+        <v>0.0504651856554921</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6435,10 +6435,10 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>51.17605553808396</v>
+        <v>51.17605555060025</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>18.98716016152298</v>
+        <v>18.98716014204102</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>0.6870333394050192</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.2196645961167539</v>
+        <v>0.2196645961476655</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>389.2271840409568</v>
+        <v>389.2271840409566</v>
       </c>
       <c r="E114" s="2" t="n">
         <v>9.67</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>48.43119133848273</v>
+        <v>48.43119120794173</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>13.20858865842902</v>
+        <v>13.20858866639889</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>0.6101795855042377</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0140184630864953</v>
+        <v>0.0140184630967988</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>49.71148330163698</v>
+        <v>49.71148325294623</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>18.18330682505362</v>
+        <v>18.18330682004276</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>0.9306607521674056</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.0109301740557289</v>
+        <v>-0.0109301739630017</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>48.61805694980904</v>
+        <v>48.61805692638903</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>12.6594521597729</v>
+        <v>12.65945220952729</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.4184160990102532</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.2175193444411434</v>
+        <v>0.2175193446059899</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>39.65848808087932</v>
+        <v>39.65848807955091</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>10.45122733783864</v>
+        <v>10.45122725324344</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>0.038192879104848</v>
@@ -6686,7 +6686,7 @@
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>369.9798774787034</v>
+        <v>369.9798774787037</v>
       </c>
       <c r="E118" s="2" t="n">
         <v>229</v>
@@ -6700,10 +6700,10 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>47.43402337444699</v>
+        <v>47.43402357428575</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>17.46256510761723</v>
+        <v>17.46256498564397</v>
       </c>
       <c r="J118" s="2" t="n">
         <v>1.702961328410952</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.2404412045011221</v>
+        <v>-0.2404412065617102</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6753,10 +6753,10 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>50.61270932571792</v>
+        <v>50.61270933971593</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>16.03746352917972</v>
+        <v>16.03746356502582</v>
       </c>
       <c r="J119" s="2" t="n">
         <v>0.7056470681139312</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.0646769324592817</v>
+        <v>0.06467693243867779</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>366.1064738824257</v>
+        <v>366.1064738824258</v>
       </c>
       <c r="E120" s="2" t="n">
         <v>30.1</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>41.07297924089076</v>
+        <v>41.07297912120058</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>12.09259515649107</v>
+        <v>12.09259515269681</v>
       </c>
       <c r="J120" s="2" t="n">
         <v>0.5389359678963249</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.014196592415851</v>
+        <v>-0.0141965923643388</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>46.50370980916971</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>13.55147718971885</v>
+        <v>13.55147718452097</v>
       </c>
       <c r="J121" s="2" t="n">
         <v>0.5118158280756434</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.2021242259928568</v>
+        <v>-0.2021242259207381</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6912,10 +6912,10 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>52.53734046884927</v>
+        <v>52.53734066836684</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>12.29689918822975</v>
+        <v>12.29689918251802</v>
       </c>
       <c r="J122" s="2" t="n">
         <v>0.7426250570269003</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.0113127427911034</v>
+        <v>0.0113127428014059</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>44.97889395734995</v>
+        <v>44.97889387683358</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>9.983763053016911</v>
+        <v>9.983763208373423</v>
       </c>
       <c r="J123" s="2" t="n">
         <v>0.3467264210444974</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.0721151929501512</v>
+        <v>-0.0721151928471178</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>362.2256499528781</v>
+        <v>362.2256499528782</v>
       </c>
       <c r="E124" s="2" t="n">
         <v>250.5</v>
@@ -7018,10 +7018,10 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>49.30811586999853</v>
+        <v>49.3081159763493</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>7.249403041406949</v>
+        <v>7.249403041406954</v>
       </c>
       <c r="J124" s="2" t="n">
         <v>1.099863231569776</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.3088042534708153</v>
+        <v>0.3088042531617255</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7071,10 +7071,10 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>47.68607657764721</v>
+        <v>47.68607658980889</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>22.69735776934501</v>
+        <v>22.69735780471711</v>
       </c>
       <c r="J125" s="2" t="n">
         <v>0.3871059167290248</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.3079628662568904</v>
+        <v>-0.3079628661332562</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>45.94333957040544</v>
+        <v>45.94333969141045</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>7.384037274696592</v>
+        <v>7.384037608498267</v>
       </c>
       <c r="J126" s="2" t="n">
         <v>0.4300092493290564</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.086106541913417</v>
+        <v>-0.0861065419978998</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7177,10 +7177,10 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>50.13110004035173</v>
+        <v>50.1311000683123</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>19.2100005685903</v>
+        <v>19.21000059942656</v>
       </c>
       <c r="J127" s="2" t="n">
         <v>0.6147092808024838</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.2158702221598007</v>
+        <v>0.2158702221804067</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>48.78450304866692</v>
+        <v>48.7845030537132</v>
       </c>
       <c r="I128" s="2" t="n">
         <v>10.64726300273618</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.5120439185532696</v>
+        <v>-0.5120439186047847</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>350.3050353864128</v>
+        <v>350.3050353864127</v>
       </c>
       <c r="E129" s="2" t="n">
         <v>117</v>
@@ -7283,10 +7283,10 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>44.26553593287758</v>
+        <v>44.26553594302876</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>8.333557246905098</v>
+        <v>8.333557304711665</v>
       </c>
       <c r="J129" s="2" t="n">
         <v>0.5946194877788219</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.0339506075669748</v>
+        <v>-0.0339506076493889</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>348.0089477010199</v>
+        <v>348.0089477010198</v>
       </c>
       <c r="E130" s="2" t="n">
         <v>58.4</v>
@@ -7336,10 +7336,10 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>49.71745156355868</v>
+        <v>49.71745155885346</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>11.53760956746602</v>
+        <v>11.53760953768261</v>
       </c>
       <c r="J130" s="2" t="n">
         <v>0.3479691560602109</v>
@@ -7354,7 +7354,7 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>-0.1655498241427909</v>
+        <v>-0.1655498243076398</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
@@ -7389,10 +7389,10 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>51.00032233306401</v>
+        <v>51.00032226206465</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>16.00173691353102</v>
+        <v>16.00173687751858</v>
       </c>
       <c r="J131" s="2" t="n">
         <v>0.3873651985363849</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>0.1405887842943765</v>
+        <v>0.1405887854276899</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7442,10 +7442,10 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>43.10609173581494</v>
+        <v>43.10609172934429</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>7.11828896501618</v>
+        <v>7.118288930334727</v>
       </c>
       <c r="J132" s="2" t="n">
         <v>0.3981754637212197</v>
@@ -7460,7 +7460,7 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>-0.0518865211751247</v>
+        <v>-0.051886521133913</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>343.7976980910776</v>
+        <v>343.7976980910779</v>
       </c>
       <c r="E133" s="2" t="n">
         <v>36.65</v>
@@ -7495,10 +7495,10 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>45.21847576266646</v>
+        <v>45.21847581071032</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>14.09640843682708</v>
+        <v>14.09640859247726</v>
       </c>
       <c r="J133" s="2" t="n">
         <v>0.4150841048666404</v>
@@ -7513,7 +7513,7 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-0.2028060466849495</v>
+        <v>-0.2028060467364698</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v/>
       </c>
       <c r="D134" s="2" t="n">
-        <v>337.4665170043825</v>
+        <v>337.4665170043828</v>
       </c>
       <c r="E134" s="2" t="n">
         <v>325.5</v>
@@ -7548,7 +7548,7 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>41.38475376024773</v>
+        <v>41.38475378927355</v>
       </c>
       <c r="I134" s="2" t="n">
         <v>14.47439686956891</v>
@@ -7566,7 +7566,7 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>-2.915678195383443</v>
+        <v>-2.915678196001572</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
@@ -7601,10 +7601,10 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>32.88210432087419</v>
+        <v>32.88210439961428</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>33.43226006851581</v>
+        <v>33.43226012270082</v>
       </c>
       <c r="J135" s="2" t="n">
         <v>1.834539006138045</v>
@@ -7619,7 +7619,7 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>-0.0304747282185828</v>
+        <v>-0.0304747280537436</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
@@ -7654,10 +7654,10 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>52.91354287242876</v>
+        <v>52.91354289654829</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>20.21572792879023</v>
+        <v>20.21572794108632</v>
       </c>
       <c r="J136" s="2" t="n">
         <v>0.6405973930851686</v>
@@ -7693,7 +7693,7 @@
         <v/>
       </c>
       <c r="D137" s="2" t="n">
-        <v>317.0174034717079</v>
+        <v>317.0174034717078</v>
       </c>
       <c r="E137" s="2" t="n">
         <v>14.35</v>
@@ -7707,10 +7707,10 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>49.79100331079432</v>
+        <v>49.79100336649218</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>15.32618203703922</v>
+        <v>15.32618203703923</v>
       </c>
       <c r="J137" s="2" t="n">
         <v>1.053058524218219</v>
@@ -7725,7 +7725,7 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>0.08112600774927101</v>
+        <v>0.0811260077389675</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>316.3815120449588</v>
+        <v>316.3815120449592</v>
       </c>
       <c r="E138" s="2" t="n">
         <v>30.3</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>40.83545530983375</v>
+        <v>40.83545534561726</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>22.59084811803288</v>
+        <v>22.59084815196244</v>
       </c>
       <c r="J138" s="2" t="n">
         <v>0.3436478742530559</v>
@@ -7778,7 +7778,7 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>-0.09988903013744981</v>
+        <v>-0.0998890300756342</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
@@ -7813,10 +7813,10 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>44.01410501162177</v>
+        <v>44.01410505795341</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>23.6996549495282</v>
+        <v>23.69965497112572</v>
       </c>
       <c r="J139" s="2" t="n">
         <v>0.4435084756874653</v>
@@ -7831,7 +7831,7 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>0.266414306847605</v>
+        <v>0.2664143067548825</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
@@ -7866,10 +7866,10 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>38.98629740318256</v>
+        <v>38.98629750459426</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>12.48245272275689</v>
+        <v>12.48245281135796</v>
       </c>
       <c r="J140" s="2" t="n">
         <v>3.660724697872062</v>
@@ -7884,7 +7884,7 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>-0.0422462476721113</v>
+        <v>-0.0422462477133246</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>21.85217834819237</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>34.21264413224542</v>
+        <v>34.21264416882679</v>
       </c>
       <c r="J141" s="2" t="n">
         <v>1.531426395068865</v>
@@ -7937,7 +7937,7 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>-0.1276691292759746</v>
+        <v>-0.1276691292347607</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
@@ -7972,10 +7972,10 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>43.91907276560795</v>
+        <v>43.9190727375445</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>8.25881905779649</v>
+        <v>8.258819054099675</v>
       </c>
       <c r="J142" s="2" t="n">
         <v>1.91701807120357</v>
@@ -7990,7 +7990,7 @@
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>0.0234624662468527</v>
+        <v>0.0234624665044195</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
@@ -8025,10 +8025,10 @@
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>49.90043188463292</v>
+        <v>49.90043192146602</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>21.06463793618489</v>
+        <v>21.06463788767577</v>
       </c>
       <c r="J143" s="2" t="n">
         <v>0.3086668838448009</v>
@@ -8043,7 +8043,7 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>-0.0553202999664241</v>
+        <v>-0.0553202999870269</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>49.72603473744199</v>
+        <v>49.72603491924094</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>17.46644296007217</v>
+        <v>17.46644296007218</v>
       </c>
       <c r="J144" s="2" t="n">
         <v>0.2441666605462811</v>
@@ -8096,7 +8096,7 @@
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>0.2451931474525255</v>
+        <v>0.2451931473701091</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
@@ -8131,10 +8131,10 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>59.61232677120285</v>
+        <v>59.6123268297131</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>16.80071786749454</v>
+        <v>16.80071789255873</v>
       </c>
       <c r="J145" s="2" t="n">
         <v>0.1469916463516673</v>
@@ -8149,7 +8149,7 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>0.0547531378758974</v>
+        <v>0.0547531379171005</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v/>
       </c>
       <c r="D146" s="2" t="n">
-        <v>299.6494788328529</v>
+        <v>299.649478832853</v>
       </c>
       <c r="E146" s="2" t="n">
         <v>104.5</v>
@@ -8184,10 +8184,10 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>44.78854859194683</v>
+        <v>44.78854831074804</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>16.87800288841239</v>
+        <v>16.87800329305433</v>
       </c>
       <c r="J146" s="2" t="n">
         <v>0.4884713842312498</v>
@@ -8202,7 +8202,7 @@
         <v>-1</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>-0.2323917780657386</v>
+        <v>-0.2323917768293776</v>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>46.07983709287873</v>
+        <v>46.07983727551901</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>7.213975821624777</v>
+        <v>7.213975826542583</v>
       </c>
       <c r="J147" s="2" t="n">
         <v>0.4300467989546897</v>
@@ -8255,7 +8255,7 @@
         <v>-1</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>0.0416307180417415</v>
+        <v>0.0416307180520452</v>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
@@ -8290,10 +8290,10 @@
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>33.41257587921132</v>
+        <v>33.41257581061124</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>23.03601382636728</v>
+        <v>23.03601375637087</v>
       </c>
       <c r="J148" s="2" t="n">
         <v>0.6095067658596406</v>
@@ -8308,7 +8308,7 @@
         <v>-1</v>
       </c>
       <c r="N148" s="2" t="n">
-        <v>-0.0336014544441489</v>
+        <v>-0.0336014544647551</v>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
@@ -8343,10 +8343,10 @@
         <v>0</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>50.16480087354284</v>
+        <v>50.16480096350729</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>18.18097253448113</v>
+        <v>18.18097254486856</v>
       </c>
       <c r="J149" s="2" t="n">
         <v>0.2813623032640251</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>46.39143338564831</v>
+        <v>46.39143337799718</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>17.32208867644708</v>
+        <v>17.3220885940055</v>
       </c>
       <c r="J150" s="2" t="n">
         <v>0.3126835443729575</v>
@@ -8414,7 +8414,7 @@
         <v>-1</v>
       </c>
       <c r="N150" s="2" t="n">
-        <v>-0.2178087264240814</v>
+        <v>-0.2178087263725674</v>
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v/>
       </c>
       <c r="D151" s="2" t="n">
-        <v>293.8202955179403</v>
+        <v>293.8202955179299</v>
       </c>
       <c r="E151" s="2" t="n">
         <v>66.3</v>
@@ -8449,10 +8449,10 @@
         <v>0</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>43.05611585001866</v>
+        <v>43.05611625559468</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>8.276045904490488</v>
+        <v>8.2760459208308</v>
       </c>
       <c r="J151" s="2" t="n">
         <v>0.4430994316632365</v>
@@ -8467,7 +8467,7 @@
         <v>-1</v>
       </c>
       <c r="N151" s="2" t="n">
-        <v>-0.0384966821075706</v>
+        <v>-0.0384966818603015</v>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
@@ -8502,10 +8502,10 @@
         <v>0</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>50.66906453764687</v>
+        <v>50.66906457714637</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>18.13931464742995</v>
+        <v>18.13931467722698</v>
       </c>
       <c r="J152" s="2" t="n">
         <v>0.2932420045283603</v>
@@ -8520,7 +8520,7 @@
         <v>-1</v>
       </c>
       <c r="N152" s="2" t="n">
-        <v>-0.0601606934398146</v>
+        <v>-0.0601606933367848</v>
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>51.10893123465441</v>
+        <v>51.10893124844115</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>7.166897420393458</v>
+        <v>7.166897415658497</v>
       </c>
       <c r="J153" s="2" t="n">
         <v>0.2683624441953413</v>
@@ -8573,7 +8573,7 @@
         <v>-1</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>-0.0424887149611204</v>
+        <v>-0.0424887150229378</v>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
@@ -8608,10 +8608,10 @@
         <v>0</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>37.79627523475769</v>
+        <v>37.79627513392064</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>12.18654919264632</v>
+        <v>12.18654919010707</v>
       </c>
       <c r="J154" s="2" t="n">
         <v>0.9389514694319364</v>
@@ -8626,7 +8626,7 @@
         <v>-1</v>
       </c>
       <c r="N154" s="2" t="n">
-        <v>-0.098168937188473</v>
+        <v>-0.0981689371472616</v>
       </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
         <v/>
       </c>
       <c r="D155" s="2" t="n">
-        <v>278.1928613302355</v>
+        <v>278.1928613302352</v>
       </c>
       <c r="E155" s="2" t="n">
         <v>59.9</v>
@@ -8661,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>36.82185966909597</v>
+        <v>36.82185975334468</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>19.02718502475542</v>
+        <v>19.0271850157013</v>
       </c>
       <c r="J155" s="2" t="n">
         <v>0.6679781366659928</v>
@@ -8679,7 +8679,7 @@
         <v>-1</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>-0.320056399057865</v>
+        <v>-0.3200563991814966</v>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v/>
       </c>
       <c r="D156" s="2" t="n">
-        <v>276.1365291991502</v>
+        <v>276.1365291991505</v>
       </c>
       <c r="E156" s="2" t="n">
         <v>18.3</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>37.65495866058095</v>
+        <v>37.65495781493803</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>23.25112174122626</v>
+        <v>23.25112250903235</v>
       </c>
       <c r="J156" s="2" t="n">
         <v>0.4909304262604738</v>
@@ -8732,7 +8732,7 @@
         <v>-1</v>
       </c>
       <c r="N156" s="2" t="n">
-        <v>-0.0030942715506364</v>
+        <v>-0.0030942710045833</v>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
@@ -8767,10 +8767,10 @@
         <v>0</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>47.93335548096283</v>
+        <v>47.93335537159861</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>15.00694244082057</v>
+        <v>15.00694246103483</v>
       </c>
       <c r="J157" s="2" t="n">
         <v>0.3044185212777047</v>
@@ -8785,7 +8785,7 @@
         <v>-1</v>
       </c>
       <c r="N157" s="2" t="n">
-        <v>-0.08182125032966039</v>
+        <v>-0.0818212502472358</v>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
@@ -8820,10 +8820,10 @@
         <v>0</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>34.83452024826683</v>
+        <v>34.83452000783616</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>25.61315383003246</v>
+        <v>25.6131539198221</v>
       </c>
       <c r="J158" s="2" t="n">
         <v>0.6226553413831123</v>
@@ -8838,7 +8838,7 @@
         <v>-1</v>
       </c>
       <c r="N158" s="2" t="n">
-        <v>0.009948146759024499</v>
+        <v>0.009948147041542999</v>
       </c>
       <c r="O158" s="2" t="inlineStr">
         <is>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>44.38550198573972</v>
+        <v>44.38550197339418</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>12.95122348633844</v>
+        <v>12.95122343533762</v>
       </c>
       <c r="J159" s="2" t="n">
         <v>0.5680360573588202</v>
@@ -8891,7 +8891,7 @@
         <v>-1</v>
       </c>
       <c r="N159" s="2" t="n">
-        <v>-0.2069607725586841</v>
+        <v>-0.2069607725174727</v>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
@@ -8926,10 +8926,10 @@
         <v>0</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>46.61564061347048</v>
+        <v>46.6156406147085</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>11.90375290376895</v>
+        <v>11.90375285181794</v>
       </c>
       <c r="J160" s="2" t="n">
         <v>0.3262805599426621</v>
@@ -8944,7 +8944,7 @@
         <v>-1</v>
       </c>
       <c r="N160" s="2" t="n">
-        <v>-0.0441944252755297</v>
+        <v>-0.044194425279651</v>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v/>
       </c>
       <c r="D161" s="2" t="n">
-        <v>265.1653978923814</v>
+        <v>265.1653978923809</v>
       </c>
       <c r="E161" s="2" t="n">
         <v>14.3</v>
@@ -8979,10 +8979,10 @@
         <v>0</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>19.85622827725571</v>
+        <v>19.85622801260527</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>44.95169428259935</v>
+        <v>44.95169432297851</v>
       </c>
       <c r="J161" s="2" t="n">
         <v>0.4152802232716628</v>
@@ -8997,7 +8997,7 @@
         <v>-1</v>
       </c>
       <c r="N161" s="2" t="n">
-        <v>-0.1156671982529704</v>
+        <v>-0.1156671980881263</v>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>43.28155235661927</v>
+        <v>43.28155236381176</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>10.9195868225472</v>
+        <v>10.91958685989384</v>
       </c>
       <c r="J162" s="2" t="n">
         <v>0.5618411130105642</v>
@@ -9071,7 +9071,7 @@
         <v/>
       </c>
       <c r="D163" s="2" t="n">
-        <v>261.5684291812595</v>
+        <v>261.5684291812596</v>
       </c>
       <c r="E163" s="2" t="n">
         <v>127</v>
@@ -9088,7 +9088,7 @@
         <v>33.15989174824841</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>27.65951630346373</v>
+        <v>27.65951633641658</v>
       </c>
       <c r="J163" s="2" t="n">
         <v>0.7963151488920598</v>
@@ -9103,7 +9103,7 @@
         <v>-1</v>
       </c>
       <c r="N163" s="2" t="n">
-        <v>0.1922291049318474</v>
+        <v>0.1922291050348654</v>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
@@ -9138,10 +9138,10 @@
         <v>0</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>38.2858780686424</v>
+        <v>38.28587776960541</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>28.58080909389904</v>
+        <v>28.58080933511681</v>
       </c>
       <c r="J164" s="2" t="n">
         <v>0.327722385491702</v>
@@ -9156,7 +9156,7 @@
         <v>-1</v>
       </c>
       <c r="N164" s="2" t="n">
-        <v>-0.0634276350218148</v>
+        <v>-0.0634276348981764</v>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v/>
       </c>
       <c r="D165" s="2" t="n">
-        <v>254.4511128865725</v>
+        <v>254.4511128865726</v>
       </c>
       <c r="E165" s="2" t="n">
         <v>22.35</v>
@@ -9191,7 +9191,7 @@
         <v>0</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>53.22524062696399</v>
+        <v>53.22524068793504</v>
       </c>
       <c r="I165" s="2" t="n">
         <v>16.05435642054467</v>
@@ -9209,7 +9209,7 @@
         <v>-1</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>-0.0056878468346041</v>
+        <v>-0.005687846844907</v>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>47.88657379029307</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>13.61798479808561</v>
+        <v>13.61798492462756</v>
       </c>
       <c r="J166" s="2" t="n">
         <v>0.4888223862630728</v>
@@ -9262,7 +9262,7 @@
         <v>-1</v>
       </c>
       <c r="N166" s="2" t="n">
-        <v>0.1164138009013516</v>
+        <v>0.1164138010043814</v>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
@@ -9297,10 +9297,10 @@
         <v>0</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>31.51943721150884</v>
+        <v>31.51943718255504</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>27.62769005718535</v>
+        <v>27.62769005718534</v>
       </c>
       <c r="J167" s="2" t="n">
         <v>0.4906193179285295</v>
@@ -9336,7 +9336,7 @@
         <v/>
       </c>
       <c r="D168" s="2" t="n">
-        <v>250.7705083261859</v>
+        <v>250.770508326186</v>
       </c>
       <c r="E168" s="2" t="n">
         <v>41.1</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>41.3773804401158</v>
+        <v>41.37738032555497</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>15.98533557759455</v>
+        <v>15.9853355870386</v>
       </c>
       <c r="J168" s="2" t="n">
         <v>1.13237468106942</v>
@@ -9368,7 +9368,7 @@
         <v>-1</v>
       </c>
       <c r="N168" s="2" t="n">
-        <v>-0.0568024629179168</v>
+        <v>-0.0568024628663995</v>
       </c>
       <c r="O168" s="2" t="inlineStr">
         <is>
@@ -9403,10 +9403,10 @@
         <v>0</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>41.97282620546793</v>
+        <v>41.97282623080326</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>17.44987797420591</v>
+        <v>17.44987795406278</v>
       </c>
       <c r="J169" s="2" t="n">
         <v>0.3271654816080007</v>
@@ -9421,7 +9421,7 @@
         <v>-1</v>
       </c>
       <c r="N169" s="2" t="n">
-        <v>0.2434543139153531</v>
+        <v>0.2434543140183911</v>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v/>
       </c>
       <c r="D170" s="2" t="n">
-        <v>248.2973429937346</v>
+        <v>248.2973429937335</v>
       </c>
       <c r="E170" s="2" t="n">
         <v>16.8</v>
@@ -9456,10 +9456,10 @@
         <v>0</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>40.01952161377513</v>
+        <v>40.01952159475276</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>14.65886036836266</v>
+        <v>14.65886038180688</v>
       </c>
       <c r="J170" s="2" t="n">
         <v>0.1876157310555101</v>
@@ -9474,7 +9474,7 @@
         <v>-1</v>
       </c>
       <c r="N170" s="2" t="n">
-        <v>-0.0675000171764023</v>
+        <v>-0.0675000171693389</v>
       </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>19.77161964921068</v>
+        <v>19.77161971743704</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>30.56348488057661</v>
+        <v>30.56348487737748</v>
       </c>
       <c r="J171" s="2" t="n">
         <v>1.194434051419669</v>
@@ -9527,7 +9527,7 @@
         <v>-1</v>
       </c>
       <c r="N171" s="2" t="n">
-        <v>-0.1480298884530346</v>
+        <v>-0.1480298883809147</v>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v/>
       </c>
       <c r="D172" s="2" t="n">
-        <v>246.7177511582574</v>
+        <v>246.7177511585017</v>
       </c>
       <c r="E172" s="2" t="n">
         <v>12.9</v>
@@ -9562,7 +9562,7 @@
         <v>0</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>50.80994463678982</v>
+        <v>50.80994462965098</v>
       </c>
       <c r="I172" s="2" t="n">
         <v>10.19491632796505</v>
@@ -9580,7 +9580,7 @@
         <v>-1</v>
       </c>
       <c r="N172" s="2" t="n">
-        <v>0.1848263514687095</v>
+        <v>0.1848263514893151</v>
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
@@ -9615,10 +9615,10 @@
         <v>0</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>48.43936829680465</v>
+        <v>48.43936829582523</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>9.498431245386906</v>
+        <v>9.498431248162378</v>
       </c>
       <c r="J173" s="2" t="n">
         <v>0.2267840506444642</v>
@@ -9633,7 +9633,7 @@
         <v>-1</v>
       </c>
       <c r="N173" s="2" t="n">
-        <v>-1.43697296496325</v>
+        <v>-1.436972964901436</v>
       </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         <v>-1</v>
       </c>
       <c r="N174" s="2" t="n">
-        <v>0.0061180969491561</v>
+        <v>0.0061180969594615</v>
       </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
@@ -9721,10 +9721,10 @@
         <v>0</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>42.90005907489014</v>
+        <v>42.90005902889149</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>19.48817083247811</v>
+        <v>19.48817087745336</v>
       </c>
       <c r="J175" s="2" t="n">
         <v>0.3376944491020122</v>
@@ -9739,7 +9739,7 @@
         <v>-1</v>
       </c>
       <c r="N175" s="2" t="n">
-        <v>0.0001695831926413</v>
+        <v>0.00016958322355</v>
       </c>
       <c r="O175" s="2" t="inlineStr">
         <is>
@@ -9774,10 +9774,10 @@
         <v>0</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>40.41457480416429</v>
+        <v>40.4145749155463</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>8.446076595228048</v>
+        <v>8.44607680504121</v>
       </c>
       <c r="J176" s="2" t="n">
         <v>0.8263576466485606</v>
@@ -9792,7 +9792,7 @@
         <v>-1</v>
       </c>
       <c r="N176" s="2" t="n">
-        <v>-0.0313130615637951</v>
+        <v>-0.0313130615843993</v>
       </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>44.56258259449277</v>
+        <v>44.56258294990131</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>8.491449507756975</v>
+        <v>8.491449518106908</v>
       </c>
       <c r="J177" s="2" t="n">
         <v>0.2258946455770647</v>
@@ -9845,7 +9845,7 @@
         <v>-1</v>
       </c>
       <c r="N177" s="2" t="n">
-        <v>0.0352914634706728</v>
+        <v>0.03529146346037</v>
       </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v/>
       </c>
       <c r="D178" s="2" t="n">
-        <v>222.6856968359984</v>
+        <v>222.6856968359988</v>
       </c>
       <c r="E178" s="2" t="n">
         <v>23.5</v>
@@ -9880,10 +9880,10 @@
         <v>0</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>40.29712276601792</v>
+        <v>40.29712208635035</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>11.09057544478218</v>
+        <v>11.09057590254906</v>
       </c>
       <c r="J178" s="2" t="n">
         <v>0.2790754089566874</v>
@@ -9898,7 +9898,7 @@
         <v>-1</v>
       </c>
       <c r="N178" s="2" t="n">
-        <v>0.0292261348782445</v>
+        <v>0.0292261354861187</v>
       </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
@@ -9933,10 +9933,10 @@
         <v>0</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>36.34722970462995</v>
+        <v>36.34722971683986</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>14.33119546250476</v>
+        <v>14.33119567315342</v>
       </c>
       <c r="J179" s="2" t="n">
         <v>1.066381790652343</v>
@@ -9951,7 +9951,7 @@
         <v>-1</v>
       </c>
       <c r="N179" s="2" t="n">
-        <v>-0.1249882091306723</v>
+        <v>-0.1249882091100648</v>
       </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>50.33532403634337</v>
+        <v>50.33532377257138</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>11.6923297363398</v>
+        <v>11.69232978433812</v>
       </c>
       <c r="J180" s="2" t="n">
         <v>0.7463375429987635</v>
@@ -10004,7 +10004,7 @@
         <v>-1</v>
       </c>
       <c r="N180" s="2" t="n">
-        <v>-0.0112427265297009</v>
+        <v>-0.0112427263339436</v>
       </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
@@ -10039,10 +10039,10 @@
         <v>0</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>42.51816092033596</v>
+        <v>42.51816084920185</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>8.833714872336341</v>
+        <v>8.83371496209886</v>
       </c>
       <c r="J181" s="2" t="n">
         <v>0.3568950648104319</v>
@@ -10057,7 +10057,7 @@
         <v>-1</v>
       </c>
       <c r="N181" s="2" t="n">
-        <v>-0.0805875279133849</v>
+        <v>-0.0805875278103623</v>
       </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v/>
       </c>
       <c r="D182" s="2" t="n">
-        <v>218.3230490209814</v>
+        <v>218.3230490209815</v>
       </c>
       <c r="E182" s="2" t="n">
         <v>52.8</v>
@@ -10092,7 +10092,7 @@
         <v>0</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>42.10845277326557</v>
+        <v>42.10845270627996</v>
       </c>
       <c r="I182" s="2" t="n">
         <v>15.31946066357615</v>
@@ -10110,7 +10110,7 @@
         <v>-1</v>
       </c>
       <c r="N182" s="2" t="n">
-        <v>0.0341173044429675</v>
+        <v>0.0341173045459987</v>
       </c>
       <c r="O182" s="2" t="inlineStr">
         <is>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>44.5487720396786</v>
+        <v>44.54877195211083</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>9.549058443256571</v>
+        <v>9.54905844676875</v>
       </c>
       <c r="J183" s="2" t="n">
         <v>1.108175109327435</v>
@@ -10163,7 +10163,7 @@
         <v>-1</v>
       </c>
       <c r="N183" s="2" t="n">
-        <v>0.0109897691194846</v>
+        <v>0.0109897691503939</v>
       </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
@@ -10198,10 +10198,10 @@
         <v>0</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>46.9187435753033</v>
+        <v>46.91874355521197</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>18.69791059847018</v>
+        <v>18.69791066219834</v>
       </c>
       <c r="J184" s="2" t="n">
         <v>0.2932155906473512</v>
@@ -10216,7 +10216,7 @@
         <v>-1</v>
       </c>
       <c r="N184" s="2" t="n">
-        <v>-0.0576333775737168</v>
+        <v>-0.0576333775531127</v>
       </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v/>
       </c>
       <c r="D185" s="2" t="n">
-        <v>214.8463789887549</v>
+        <v>214.8463789887551</v>
       </c>
       <c r="E185" s="2" t="n">
         <v>40.1</v>
@@ -10251,10 +10251,10 @@
         <v>0</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>27.20632174789856</v>
+        <v>27.20632159837983</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>23.74693363638758</v>
+        <v>23.74693377492897</v>
       </c>
       <c r="J185" s="2" t="n">
         <v>0.9764974482943862</v>
@@ -10269,7 +10269,7 @@
         <v>-1</v>
       </c>
       <c r="N185" s="2" t="n">
-        <v>-0.0634739213691552</v>
+        <v>-0.06347392131763931</v>
       </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>45.26495025920885</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>16.62448662407959</v>
+        <v>16.62448660250135</v>
       </c>
       <c r="J186" s="2" t="n">
         <v>0.3039521839179221</v>
@@ -10322,7 +10322,7 @@
         <v>-1</v>
       </c>
       <c r="N186" s="2" t="n">
-        <v>0.105424079806361</v>
+        <v>0.1054240798887905</v>
       </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
@@ -10357,10 +10357,10 @@
         <v>0</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>27.17393861791064</v>
+        <v>27.17393866854364</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>30.03025003114105</v>
+        <v>30.03025002327737</v>
       </c>
       <c r="J187" s="2" t="n">
         <v>0.4642924066341629</v>
@@ -10375,7 +10375,7 @@
         <v>-1</v>
       </c>
       <c r="N187" s="2" t="n">
-        <v>-0.1358970078377301</v>
+        <v>-0.1358970078995505</v>
       </c>
       <c r="O187" s="2" t="inlineStr">
         <is>
@@ -10410,10 +10410,10 @@
         <v>0</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>39.5579646028396</v>
+        <v>39.55796453620219</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>30.95033980360797</v>
+        <v>30.9503398730786</v>
       </c>
       <c r="J188" s="2" t="n">
         <v>0.5475753568208963</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>38.52538074847924</v>
+        <v>38.52538069981038</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>18.72159288004454</v>
+        <v>18.72159302725533</v>
       </c>
       <c r="J189" s="2" t="n">
         <v>0.5836209296933674</v>
@@ -10481,7 +10481,7 @@
         <v>-1</v>
       </c>
       <c r="N189" s="2" t="n">
-        <v>-0.0356502124082291</v>
+        <v>-0.0356502113779289</v>
       </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>0</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>39.3540259648052</v>
+        <v>39.35402593274753</v>
       </c>
       <c r="I190" s="2" t="n">
         <v>43.1854500495317</v>
@@ -10534,7 +10534,7 @@
         <v>-1</v>
       </c>
       <c r="N190" s="2" t="n">
-        <v>-0.0026285838325871</v>
+        <v>-0.002628583822285</v>
       </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
@@ -10569,10 +10569,10 @@
         <v>0</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>33.69390224805949</v>
+        <v>33.69390238683447</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>31.51262474302572</v>
+        <v>31.51262466019424</v>
       </c>
       <c r="J191" s="2" t="n">
         <v>0.2854353718268232</v>
@@ -10587,7 +10587,7 @@
         <v>-1</v>
       </c>
       <c r="N191" s="2" t="n">
-        <v>-0.0025094317893191</v>
+        <v>-0.0025094317790181</v>
       </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>40.06686551843293</v>
+        <v>40.06686576937425</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>15.45738394249638</v>
+        <v>15.4573839128141</v>
       </c>
       <c r="J192" s="2" t="n">
         <v>0.229060249452474</v>
@@ -10640,7 +10640,7 @@
         <v>-1</v>
       </c>
       <c r="N192" s="2" t="n">
-        <v>-0.0833433793510652</v>
+        <v>-0.0833433793098548</v>
       </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>0</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>44.69649717164785</v>
+        <v>44.69649728456474</v>
       </c>
       <c r="I193" s="2" t="n">
         <v>9.943667066300442</v>
@@ -10714,7 +10714,7 @@
         <v/>
       </c>
       <c r="D194" s="2" t="n">
-        <v>201.4910789740254</v>
+        <v>201.4910789740253</v>
       </c>
       <c r="E194" s="2" t="n">
         <v>127.5</v>
@@ -10728,10 +10728,10 @@
         <v>0</v>
       </c>
       <c r="H194" s="2" t="n">
-        <v>38.5078148149064</v>
+        <v>38.50781473330228</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>10.86015165111809</v>
+        <v>10.86015161338558</v>
       </c>
       <c r="J194" s="2" t="n">
         <v>0.284972936575294</v>
@@ -10746,7 +10746,7 @@
         <v>-1</v>
       </c>
       <c r="N194" s="2" t="n">
-        <v>-0.3222824528311205</v>
+        <v>-0.3222824516977951</v>
       </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>0</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>28.06473914359387</v>
+        <v>28.06473921867615</v>
       </c>
       <c r="I195" s="2" t="n">
         <v>29.84273399533629</v>
@@ -10799,7 +10799,7 @@
         <v>-1</v>
       </c>
       <c r="N195" s="2" t="n">
-        <v>-0.0365417323522028</v>
+        <v>-0.0365417325376544</v>
       </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v/>
       </c>
       <c r="D196" s="2" t="n">
-        <v>197.5015108464608</v>
+        <v>197.5015108464615</v>
       </c>
       <c r="E196" s="2" t="n">
         <v>42.65</v>
@@ -10834,10 +10834,10 @@
         <v>0</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>34.85372653284045</v>
+        <v>34.85372617688648</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>25.56292787570287</v>
+        <v>25.56292777134152</v>
       </c>
       <c r="J196" s="2" t="n">
         <v>0.4103094835306995</v>
@@ -10852,7 +10852,7 @@
         <v>-1</v>
       </c>
       <c r="N196" s="2" t="n">
-        <v>0.0295921485167696</v>
+        <v>0.0295921476925375</v>
       </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
@@ -10887,10 +10887,10 @@
         <v>0</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>45.68128005965653</v>
+        <v>45.68128016917689</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>14.85909081426165</v>
+        <v>14.85909081004431</v>
       </c>
       <c r="J197" s="2" t="n">
         <v>0.8076366434013376</v>
@@ -10905,7 +10905,7 @@
         <v>-1</v>
       </c>
       <c r="N197" s="2" t="n">
-        <v>0.0561018059470849</v>
+        <v>0.0561018059294289</v>
       </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>40.19103230323058</v>
+        <v>40.19103231989841</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>11.72778855007041</v>
+        <v>11.72778874423508</v>
       </c>
       <c r="J198" s="2" t="n">
         <v>0.6395985030895536</v>
@@ -10958,7 +10958,7 @@
         <v>-1</v>
       </c>
       <c r="N198" s="2" t="n">
-        <v>-0.6922732765529094</v>
+        <v>-0.6922732766559421</v>
       </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
@@ -10993,10 +10993,10 @@
         <v>0</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>35.64838153150578</v>
+        <v>35.64838155936893</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>17.31442414663597</v>
+        <v>17.31442414883162</v>
       </c>
       <c r="J199" s="2" t="n">
         <v>0.3991155372949602</v>
@@ -11011,7 +11011,7 @@
         <v>-1</v>
       </c>
       <c r="N199" s="2" t="n">
-        <v>-0.2337598925386563</v>
+        <v>-0.2337598927035071</v>
       </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v/>
       </c>
       <c r="D200" s="2" t="n">
-        <v>193.3149661222593</v>
+        <v>193.3149661222594</v>
       </c>
       <c r="E200" s="2" t="n">
         <v>51.2</v>
@@ -11046,10 +11046,10 @@
         <v>0</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>43.29617570991837</v>
+        <v>43.29617507444954</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>12.6884011453634</v>
+        <v>12.68840139265368</v>
       </c>
       <c r="J200" s="2" t="n">
         <v>1.208019499564158</v>
@@ -11064,7 +11064,7 @@
         <v>-1</v>
       </c>
       <c r="N200" s="2" t="n">
-        <v>-0.0163680914158571</v>
+        <v>-0.0163680912098024</v>
       </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v/>
       </c>
       <c r="D201" s="2" t="n">
-        <v>191.6573189427237</v>
+        <v>191.6573189427235</v>
       </c>
       <c r="E201" s="2" t="n">
         <v>7.16</v>
@@ -11099,10 +11099,10 @@
         <v>0</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>28.16025987673622</v>
+        <v>28.1602599067357</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>34.55317400156841</v>
+        <v>34.55317404727814</v>
       </c>
       <c r="J201" s="2" t="n">
         <v>0.7792451134956063</v>
@@ -11117,7 +11117,7 @@
         <v>-1</v>
       </c>
       <c r="N201" s="2" t="n">
-        <v>-0.0145818851814869</v>
+        <v>-0.0145818851897294</v>
       </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
@@ -11152,10 +11152,10 @@
         <v>0</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>47.53131830125273</v>
+        <v>47.53131800647098</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>9.488704944640316</v>
+        <v>9.488704957308942</v>
       </c>
       <c r="J202" s="2" t="n">
         <v>1.004961942133657</v>
@@ -11170,7 +11170,7 @@
         <v>-1</v>
       </c>
       <c r="N202" s="2" t="n">
-        <v>0.0021644233973419</v>
+        <v>0.0021644234385533</v>
       </c>
       <c r="O202" s="2" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v/>
       </c>
       <c r="D203" s="2" t="n">
-        <v>184.7044355888208</v>
+        <v>184.7044355888205</v>
       </c>
       <c r="E203" s="2" t="n">
         <v>54.8</v>
@@ -11205,10 +11205,10 @@
         <v>0</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>48.10117714605607</v>
+        <v>48.10117711328621</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>11.78235090794803</v>
+        <v>11.78235092915093</v>
       </c>
       <c r="J203" s="2" t="n">
         <v>0.4750322937373114</v>
@@ -11223,7 +11223,7 @@
         <v>-1</v>
       </c>
       <c r="N203" s="2" t="n">
-        <v>-0.0320161757015037</v>
+        <v>-0.0320161754851497</v>
       </c>
       <c r="O203" s="2" t="inlineStr">
         <is>
@@ -11258,10 +11258,10 @@
         <v>0</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>37.30004592142666</v>
+        <v>37.30004592664131</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>23.51538829993409</v>
+        <v>23.51538839325224</v>
       </c>
       <c r="J204" s="2" t="n">
         <v>0.9235778656030794</v>
@@ -11276,7 +11276,7 @@
         <v>-1</v>
       </c>
       <c r="N204" s="2" t="n">
-        <v>0.0532702662001528</v>
+        <v>0.0532702661795522</v>
       </c>
       <c r="O204" s="2" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v/>
       </c>
       <c r="D205" s="2" t="n">
-        <v>177.6402550041813</v>
+        <v>177.6402550041821</v>
       </c>
       <c r="E205" s="2" t="n">
         <v>13.1</v>
@@ -11311,10 +11311,10 @@
         <v>0</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>42.94896405812856</v>
+        <v>42.94896407411456</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>10.40522768752756</v>
+        <v>10.40522774282411</v>
       </c>
       <c r="J205" s="2" t="n">
         <v>0.5857922323265699</v>
@@ -11329,7 +11329,7 @@
         <v>-1</v>
       </c>
       <c r="N205" s="2" t="n">
-        <v>-0.0060004394793497</v>
+        <v>-0.0060004394999562</v>
       </c>
       <c r="O205" s="2" t="inlineStr">
         <is>
@@ -11364,10 +11364,10 @@
         <v>0</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>48.26190980261899</v>
+        <v>48.26190797776799</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>14.46940418324942</v>
+        <v>14.46940361686635</v>
       </c>
       <c r="J206" s="2" t="n">
         <v>0.2018495804703315</v>
@@ -11382,7 +11382,7 @@
         <v>-1</v>
       </c>
       <c r="N206" s="2" t="n">
-        <v>0.0337906432101542</v>
+        <v>0.0337906437871186</v>
       </c>
       <c r="O206" s="2" t="inlineStr">
         <is>
@@ -11417,10 +11417,10 @@
         <v>0</v>
       </c>
       <c r="H207" s="2" t="n">
-        <v>31.03874498725596</v>
+        <v>31.03874514585865</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>28.9862598357252</v>
+        <v>28.98625982411211</v>
       </c>
       <c r="J207" s="2" t="n">
         <v>0.4531187577329384</v>
@@ -11435,7 +11435,7 @@
         <v>-1</v>
       </c>
       <c r="N207" s="2" t="n">
-        <v>-0.0100129085496527</v>
+        <v>-0.0100129084260165</v>
       </c>
       <c r="O207" s="2" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v/>
       </c>
       <c r="D208" s="2" t="n">
-        <v>171.9650558359568</v>
+        <v>171.9650558359567</v>
       </c>
       <c r="E208" s="2" t="n">
         <v>10.05</v>
@@ -11470,10 +11470,10 @@
         <v>0</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>46.10135436212738</v>
+        <v>46.10135441959294</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>23.78098743873543</v>
+        <v>23.78098748898774</v>
       </c>
       <c r="J208" s="2" t="n">
         <v>0.5435536924718232</v>
@@ -11488,7 +11488,7 @@
         <v>-1</v>
       </c>
       <c r="N208" s="2" t="n">
-        <v>0.0318304186032702</v>
+        <v>0.0318304186135729</v>
       </c>
       <c r="O208" s="2" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>0</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>43.19284582259632</v>
+        <v>43.19284594799116</v>
       </c>
       <c r="I209" s="2" t="n">
         <v>17.21384877116909</v>
@@ -11541,7 +11541,7 @@
         <v>-1</v>
       </c>
       <c r="N209" s="2" t="n">
-        <v>0.0845372420297703</v>
+        <v>0.0845372420091613</v>
       </c>
       <c r="O209" s="2" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v/>
       </c>
       <c r="D210" s="2" t="n">
-        <v>163.7676625484302</v>
+        <v>163.7676625484303</v>
       </c>
       <c r="E210" s="2" t="n">
         <v>18.6</v>
@@ -11576,10 +11576,10 @@
         <v>0</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>45.70987711012484</v>
+        <v>45.70987718071717</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>21.29450834468325</v>
+        <v>21.29450842750508</v>
       </c>
       <c r="J210" s="2" t="n">
         <v>0.5577451302373022</v>
@@ -11594,7 +11594,7 @@
         <v>-1</v>
       </c>
       <c r="N210" s="2" t="n">
-        <v>0.0286396185135588</v>
+        <v>0.0286396185547706</v>
       </c>
       <c r="O210" s="2" t="inlineStr">
         <is>
@@ -11629,10 +11629,10 @@
         <v>0</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>44.18405120070077</v>
+        <v>44.18405124551048</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>12.24777575381956</v>
+        <v>12.24777575394772</v>
       </c>
       <c r="J211" s="2" t="n">
         <v>0.6688221579356405</v>
@@ -11647,7 +11647,7 @@
         <v>-1</v>
       </c>
       <c r="N211" s="2" t="n">
-        <v>0.4900884812666932</v>
+        <v>0.4900884813491175</v>
       </c>
       <c r="O211" s="2" t="inlineStr">
         <is>
@@ -11682,10 +11682,10 @@
         <v>0</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>40.68928480399045</v>
+        <v>40.6892849239088</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>16.66556523742504</v>
+        <v>16.66556532989329</v>
       </c>
       <c r="J212" s="2" t="n">
         <v>0.5364844770037892</v>
@@ -11700,7 +11700,7 @@
         <v>-1</v>
       </c>
       <c r="N212" s="2" t="n">
-        <v>0.0611013943089817</v>
+        <v>0.0611013945253358</v>
       </c>
       <c r="O212" s="2" t="inlineStr">
         <is>
@@ -11735,10 +11735,10 @@
         <v>0</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>50.18903975062184</v>
+        <v>50.18903977017816</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>9.42311798228104</v>
+        <v>9.423117995100393</v>
       </c>
       <c r="J213" s="2" t="n">
         <v>0.2955774296409261</v>
@@ -11753,7 +11753,7 @@
         <v>-1</v>
       </c>
       <c r="N213" s="2" t="n">
-        <v>0.0483317752443264</v>
+        <v>0.0483317752134175</v>
       </c>
       <c r="O213" s="2" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v/>
       </c>
       <c r="D214" s="2" t="n">
-        <v>154.1474783889898</v>
+        <v>154.1474783889897</v>
       </c>
       <c r="E214" s="2" t="n">
         <v>65.7</v>
@@ -11788,10 +11788,10 @@
         <v>0</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>43.76246059537959</v>
+        <v>43.76246055210822</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>16.07455753181893</v>
+        <v>16.07455750971075</v>
       </c>
       <c r="J214" s="2" t="n">
         <v>0.2414967699645752</v>
@@ -11806,7 +11806,7 @@
         <v>-1</v>
       </c>
       <c r="N214" s="2" t="n">
-        <v>0.3903570685446809</v>
+        <v>0.3903570691628659</v>
       </c>
       <c r="O214" s="2" t="inlineStr">
         <is>
@@ -11841,10 +11841,10 @@
         <v>0</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>51.52865770854607</v>
+        <v>51.52865766084308</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>14.03417850282684</v>
+        <v>14.0341787550487</v>
       </c>
       <c r="J215" s="2" t="n">
         <v>0.430577401025805</v>
@@ -11859,7 +11859,7 @@
         <v>-1</v>
       </c>
       <c r="N215" s="2" t="n">
-        <v>-0.0024259697297314</v>
+        <v>-0.0024259696885191</v>
       </c>
       <c r="O215" s="2" t="inlineStr">
         <is>
@@ -11894,10 +11894,10 @@
         <v>0</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>44.13227426654619</v>
+        <v>44.13227421116185</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>17.18922099829703</v>
+        <v>17.18922107703016</v>
       </c>
       <c r="J216" s="2" t="n">
         <v>0.4008480980686347</v>
@@ -11912,7 +11912,7 @@
         <v>-1</v>
       </c>
       <c r="N216" s="2" t="n">
-        <v>0.1005314149145683</v>
+        <v>0.1005314151412337</v>
       </c>
       <c r="O216" s="2" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v/>
       </c>
       <c r="D217" s="2" t="n">
-        <v>140.7352802241477</v>
+        <v>140.7352802241467</v>
       </c>
       <c r="E217" s="2" t="n">
         <v>30.5</v>
@@ -11947,10 +11947,10 @@
         <v>0</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>45.445053359774</v>
+        <v>45.44505312270383</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>10.32107704248801</v>
+        <v>10.32107711949647</v>
       </c>
       <c r="J217" s="2" t="n">
         <v>0.4833812296324459</v>
@@ -11965,7 +11965,7 @@
         <v>-1</v>
       </c>
       <c r="N217" s="2" t="n">
-        <v>-0.0047931361270493</v>
+        <v>-0.0047931359003887</v>
       </c>
       <c r="O217" s="2" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v/>
       </c>
       <c r="D218" s="2" t="n">
-        <v>130.6459799459829</v>
+        <v>130.6459799459831</v>
       </c>
       <c r="E218" s="2" t="n">
         <v>38.65</v>
@@ -12000,10 +12000,10 @@
         <v>0</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>43.73409044546906</v>
+        <v>43.7340901490882</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>8.697544775588822</v>
+        <v>8.697544881961775</v>
       </c>
       <c r="J218" s="2" t="n">
         <v>0.8063415638919642</v>
@@ -12018,7 +12018,7 @@
         <v>-1</v>
       </c>
       <c r="N218" s="2" t="n">
-        <v>-0.035797262714481</v>
+        <v>-0.0357972623538789</v>
       </c>
       <c r="O218" s="2" t="inlineStr">
         <is>
@@ -12053,10 +12053,10 @@
         <v>0</v>
       </c>
       <c r="H219" s="2" t="n">
-        <v>45.66743436359746</v>
+        <v>45.6674343290638</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>16.74123230501417</v>
+        <v>16.74123241074446</v>
       </c>
       <c r="J219" s="2" t="n">
         <v>0.512368857738799</v>
@@ -12071,7 +12071,7 @@
         <v>-1</v>
       </c>
       <c r="N219" s="2" t="n">
-        <v>-0.0175156681137941</v>
+        <v>-0.0175156680725798</v>
       </c>
       <c r="O219" s="2" t="inlineStr">
         <is>
@@ -12106,10 +12106,10 @@
         <v>0</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>41.35326686781427</v>
+        <v>41.35326669938922</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>7.539948723223264</v>
+        <v>7.539948737126773</v>
       </c>
       <c r="J220" s="2" t="n">
         <v>0.6449225805125447</v>
@@ -12124,7 +12124,7 @@
         <v>-1</v>
       </c>
       <c r="N220" s="2" t="n">
-        <v>0.1667860888068355</v>
+        <v>0.1667860885389589</v>
       </c>
       <c r="O220" s="2" t="inlineStr">
         <is>
@@ -12159,10 +12159,10 @@
         <v>0</v>
       </c>
       <c r="H221" s="2" t="n">
-        <v>43.25285069589553</v>
+        <v>43.25285071510842</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>10.56043687720637</v>
+        <v>10.56043701137542</v>
       </c>
       <c r="J221" s="2" t="n">
         <v>0.4125670338351643</v>
@@ -12212,10 +12212,10 @@
         <v>0</v>
       </c>
       <c r="H222" s="2" t="n">
-        <v>38.73812674258139</v>
+        <v>38.73812671228237</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>15.67269632113529</v>
+        <v>15.67269637706898</v>
       </c>
       <c r="J222" s="2" t="n">
         <v>0.657304719552664</v>
@@ -12230,7 +12230,7 @@
         <v>-1</v>
       </c>
       <c r="N222" s="2" t="n">
-        <v>0.0117648888430679</v>
+        <v>0.0117648889151891</v>
       </c>
       <c r="O222" s="2" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v/>
       </c>
       <c r="D223" s="2" t="n">
-        <v>95.1883359933589</v>
+        <v>95.18833599335916</v>
       </c>
       <c r="E223" s="2" t="n">
         <v>75</v>
@@ -12265,10 +12265,10 @@
         <v>0</v>
       </c>
       <c r="H223" s="2" t="n">
-        <v>48.15313485408929</v>
+        <v>48.15313495795851</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>15.57708939285579</v>
+        <v>15.57708957573576</v>
       </c>
       <c r="J223" s="2" t="n">
         <v>0.2467383820565782</v>
@@ -12283,7 +12283,7 @@
         <v>-1</v>
       </c>
       <c r="N223" s="2" t="n">
-        <v>0.1664893345526055</v>
+        <v>0.1664893354798645</v>
       </c>
       <c r="O223" s="2" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v/>
       </c>
       <c r="D224" s="2" t="n">
-        <v>87.87793163510958</v>
+        <v>87.87793163510953</v>
       </c>
       <c r="E224" s="2" t="n">
         <v>6.89</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="H224" s="2" t="n">
-        <v>47.57595317317443</v>
+        <v>47.575953191365</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>11.46637745890913</v>
+        <v>11.46637751548022</v>
       </c>
       <c r="J224" s="2" t="n">
         <v>0.8483087160487637</v>
@@ -12336,7 +12336,7 @@
         <v>-1</v>
       </c>
       <c r="N224" s="2" t="n">
-        <v>0.0143153394168643</v>
+        <v>0.0143153394065619</v>
       </c>
       <c r="O224" s="2" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v/>
       </c>
       <c r="D225" s="2" t="n">
-        <v>77.73259070818116</v>
+        <v>77.73259070818115</v>
       </c>
       <c r="E225" s="2" t="n">
         <v>18.85</v>
@@ -12371,10 +12371,10 @@
         <v>0</v>
       </c>
       <c r="H225" s="2" t="n">
-        <v>44.53933614179461</v>
+        <v>44.53933603848505</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>10.5849106289298</v>
+        <v>10.58491059990386</v>
       </c>
       <c r="J225" s="2" t="n">
         <v>0.531021690819635</v>
@@ -12389,7 +12389,7 @@
         <v>-1</v>
       </c>
       <c r="N225" s="2" t="n">
-        <v>0.0211456934348042</v>
+        <v>0.0211456935481343</v>
       </c>
       <c r="O225" s="2" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v/>
       </c>
       <c r="D226" s="2" t="n">
-        <v>68.83711718211364</v>
+        <v>68.83711718211373</v>
       </c>
       <c r="E226" s="2" t="n">
         <v>87</v>
@@ -12424,10 +12424,10 @@
         <v>0</v>
       </c>
       <c r="H226" s="2" t="n">
-        <v>38.44744092122617</v>
+        <v>38.44744115990087</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>18.78726908582384</v>
+        <v>18.78726908582383</v>
       </c>
       <c r="J226" s="2" t="n">
         <v>0.2606160839931321</v>
@@ -12442,7 +12442,7 @@
         <v>-1</v>
       </c>
       <c r="N226" s="2" t="n">
-        <v>-0.1736420534423914</v>
+        <v>-0.1736420538545107</v>
       </c>
       <c r="O226" s="2" t="inlineStr">
         <is>
@@ -12477,10 +12477,10 @@
         <v>0</v>
       </c>
       <c r="H227" s="2" t="n">
-        <v>44.05277874209728</v>
+        <v>44.05277871179965</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>19.49013745811878</v>
+        <v>19.49013747977346</v>
       </c>
       <c r="J227" s="2" t="n">
         <v>0.6987844388522639</v>
@@ -12516,7 +12516,7 @@
         <v/>
       </c>
       <c r="D228" s="2" t="n">
-        <v>61.79739911523027</v>
+        <v>61.79739911523002</v>
       </c>
       <c r="E228" s="2" t="n">
         <v>18.95</v>
@@ -12530,10 +12530,10 @@
         <v>0</v>
       </c>
       <c r="H228" s="2" t="n">
-        <v>38.87319178174341</v>
+        <v>38.87319203942496</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>16.51724005631037</v>
+        <v>16.51723992337034</v>
       </c>
       <c r="J228" s="2" t="n">
         <v>0.3048480876411034</v>
@@ -12548,7 +12548,7 @@
         <v>-1</v>
       </c>
       <c r="N228" s="2" t="n">
-        <v>-0.0620486001029572</v>
+        <v>-0.0620486003296196</v>
       </c>
       <c r="O228" s="2" t="inlineStr">
         <is>

--- a/output/full_scan/batch_seq2_2026-09-24.xlsx
+++ b/output/full_scan/batch_seq2_2026-09-24.xlsx
@@ -1174,7 +1174,7 @@
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>947.2159540596946</v>
+        <v>907.2159540596946</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>77.40000000000001</v>
@@ -3177,21 +3177,21 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1815</v>
+        <v>2301</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>富喬</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>608.5170309436568</v>
+        <v>604.346243903242</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>116</v>
+        <v>287</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>50.20592836180932</v>
+        <v>53.66341765473977</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>31.51267897007891</v>
+        <v>29.5405773760245</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.4091265424535423</v>
+        <v>0.4255381368334286</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-1.896972719138102</v>
+        <v>-2.40364639860854</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>2301</v>
+        <v>2441</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>超豐</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>604.346243903242</v>
+        <v>601.6502080181851</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>287</v>
+        <v>124</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>53.66341765473977</v>
+        <v>56.93159659709492</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>29.5405773760245</v>
+        <v>16.38853723654727</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.4255381368334286</v>
+        <v>0.6563858128763391</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>1</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-2.40364639860854</v>
+        <v>1.354916534943151</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>2441</v>
+        <v>2107</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>超豐</t>
+          <t>厚生</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>601.6502080181851</v>
+        <v>599.0139968055466</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>124</v>
+        <v>26.95</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>56.93159659709492</v>
+        <v>56.19444630633507</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>16.38853723654727</v>
+        <v>23.42866125198688</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.6563858128763391</v>
+        <v>0.8317861121425919</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>1.354916534943151</v>
+        <v>-0.0218276706329851</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>2107</v>
+        <v>2421</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>厚生</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>599.0139968055466</v>
+        <v>592.6842801328203</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>26.95</v>
+        <v>167</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>56.19444630633507</v>
+        <v>56.36437442007536</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>23.42866125198688</v>
+        <v>16.98581197336325</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.8317861121425919</v>
+        <v>0.3693269264607346</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.0218276706329851</v>
+        <v>-0.8673451579435074</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>2421</v>
+        <v>2104</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>國際中橡</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>592.6842801328203</v>
+        <v>589.6716709476325</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>167</v>
+        <v>11.15</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>56.36437442007536</v>
+        <v>59.45129495411348</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>16.98581197336325</v>
+        <v>29.55860870134153</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.3693269264607346</v>
+        <v>2.201451231272236</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.8673451579435074</v>
+        <v>0.0880937764864289</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>2104</v>
+        <v>1904</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>國際中橡</t>
+          <t>正隆</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>589.6716709476325</v>
+        <v>585.9969410619888</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>11.15</v>
+        <v>24.9</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>59.45129495411348</v>
+        <v>53.87496287507386</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>29.55860870134153</v>
+        <v>28.12096990264753</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>2.201451231272236</v>
+        <v>0.6942681600017268</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.0880937764864289</v>
+        <v>-0.0679101660109234</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1904</v>
+        <v>2338</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>正隆</t>
+          <t>光罩</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>585.9969410619888</v>
+        <v>581.8562867615966</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>24.9</v>
+        <v>47.1</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>53.87496287507386</v>
+        <v>58.03948122317059</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>28.12096990264753</v>
+        <v>39.2313854154655</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.6942681600017268</v>
+        <v>0.2517450244329172</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.0679101660109234</v>
+        <v>0.2991476719303518</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>2338</v>
+        <v>2399</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>光罩</t>
+          <t>映泰</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>581.8562867615966</v>
+        <v>580.1434711704227</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>47.1</v>
+        <v>47.3</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>58.03948122317059</v>
+        <v>53.8991072324332</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>39.2313854154655</v>
+        <v>19.18509183547802</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.2517450244329172</v>
+        <v>0.3239170823003393</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.2991476719303518</v>
+        <v>-0.0179219471292723</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>2399</v>
+        <v>2424</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>映泰</t>
+          <t>隴華</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>580.1434711704227</v>
+        <v>576.4181644897611</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>47.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>53.8991072324332</v>
+        <v>49.63413613368842</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>19.18509183547802</v>
+        <v>21.40773066113696</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.3239170823003393</v>
+        <v>0.58268884415722</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.0179219471292723</v>
+        <v>0.0501257320161909</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>2424</v>
+        <v>2038</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>隴華</t>
+          <t>海光</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>576.4181644897611</v>
+        <v>571.6575452231314</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>12.55</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>49.63413613368842</v>
+        <v>54.64959770622918</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>21.40773066113696</v>
+        <v>27.54805260943758</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.58268884415722</v>
+        <v>3.476784031269073</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.0501257320161909</v>
+        <v>0.0257841614736626</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>2038</v>
+        <v>2351</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>海光</t>
+          <t>順德</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>571.6575452231314</v>
+        <v>571.4532672135879</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>12.55</v>
+        <v>219.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>54.64959770622918</v>
+        <v>47.81893156998148</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>27.54805260943758</v>
+        <v>29.57893331786734</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>3.476784031269073</v>
+        <v>0.822446880628226</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0257841614736626</v>
+        <v>-3.910376432301448</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>2351</v>
+        <v>1815</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>順德</t>
+          <t>富喬</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>571.4532672135879</v>
+        <v>568.5170309436568</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>219.5</v>
+        <v>116</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>47.81893156998148</v>
+        <v>50.20592836180932</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>29.57893331786734</v>
+        <v>31.51267897007891</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.822446880628226</v>
+        <v>0.4091265424535423</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,11 +3803,11 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-3.910376432301448</v>
+        <v>-1.896972719138102</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -5085,21 +5085,21 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>1785</v>
+        <v>2208</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>光洋科</t>
+          <t>台船</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>458.0836760282951</v>
+        <v>453.8985888713039</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>95.8</v>
+        <v>19.4</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>39.33347979389713</v>
+        <v>55.3257968146044</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>26.8883656200478</v>
+        <v>22.05186260069619</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.7104465843872415</v>
+        <v>0.7558225980049488</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.3327942130494321</v>
+        <v>0.0742220764531602</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>2208</v>
+        <v>2393</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>台船</t>
+          <t>億光</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>453.8985888713039</v>
+        <v>447.4667127234046</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>19.4</v>
+        <v>63.4</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>55.3257968146044</v>
+        <v>48.46569377816383</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>22.05186260069619</v>
+        <v>11.08529073392815</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.7558225980049488</v>
+        <v>1.300608595932826</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0742220764531602</v>
+        <v>0.0349018032715383</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>2393</v>
+        <v>1710</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>億光</t>
+          <t>東聯</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>447.4667127234046</v>
+        <v>447.1977816965119</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>63.4</v>
+        <v>16.4</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>48.46569377816383</v>
+        <v>54.66097982099056</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>11.08529073392815</v>
+        <v>26.87481327581776</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.300608595932826</v>
+        <v>0.6202075356997018</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0349018032715383</v>
+        <v>0.0283285405145085</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>1710</v>
+        <v>1614</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>東聯</t>
+          <t>三洋電</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>447.1977816965119</v>
+        <v>446.0100917828321</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>16.4</v>
+        <v>31.15</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>54.66097982099056</v>
+        <v>56.37527112948978</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>26.87481327581776</v>
+        <v>26.7161312942137</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.6202075356997018</v>
+        <v>0.5236319123987626</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.0283285405145085</v>
+        <v>0.0477903844214449</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>1614</v>
+        <v>2106</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>三洋電</t>
+          <t>建大</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>446.0100917828321</v>
+        <v>437.3727309333153</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>31.15</v>
+        <v>16.65</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>56.37527112948978</v>
+        <v>42.50155324750998</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>26.7161312942137</v>
+        <v>22.2041153467602</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.5236319123987626</v>
+        <v>0.1993209185384439</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,51 +5340,51 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0477903844214449</v>
+        <v>0.0101202395393836</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>2106</v>
+        <v>1589</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>建大</t>
+          <t>永冠-KY</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>437.3727309333153</v>
+        <v>436.2437654589683</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>16.65</v>
+        <v>5.54</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G93" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>42.50155324750998</v>
+        <v>24.03488264070512</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>22.2041153467602</v>
+        <v>38.86916791888412</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.1993209185384439</v>
+        <v>4.024376545896833</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,51 +5393,51 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0101202395393836</v>
+        <v>0.0987299345354202</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>1589</v>
+        <v>2009</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>永冠-KY</t>
+          <t>第一銅</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>436.2437654589683</v>
+        <v>435.0610665187907</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>5.54</v>
+        <v>39.15</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G94" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>24.03488264070512</v>
+        <v>47.62274020682705</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>38.86916791888412</v>
+        <v>22.63269151703244</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>4.024376545896833</v>
+        <v>0.4548821519677418</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0987299345354202</v>
+        <v>-0.0622745405603558</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>2009</v>
+        <v>1731</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>第一銅</t>
+          <t>美吾華</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>435.0610665187907</v>
+        <v>432.6730178963597</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>39.15</v>
+        <v>20.9</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>47.62274020682705</v>
+        <v>49.94539012669958</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>22.63269151703244</v>
+        <v>12.45688393393229</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.4548821519677418</v>
+        <v>0.7407744247118293</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.0622745405603558</v>
+        <v>0.003893336922151</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>1731</v>
+        <v>1717</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>美吾華</t>
+          <t>長興</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>432.6730178963597</v>
+        <v>426.9108097023167</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>20.9</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>49.94539012669958</v>
+        <v>48.37106891299786</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>12.45688393393229</v>
+        <v>9.719419490399524</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.7407744247118293</v>
+        <v>0.2905782265316657</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.003893336922151</v>
+        <v>-0.341949402108933</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>1717</v>
+        <v>2408</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>長興</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>426.9108097023167</v>
+        <v>425.0667721724499</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>71.40000000000001</v>
+        <v>503</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>48.37106891299786</v>
+        <v>50.98652261854292</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>9.719419490399524</v>
+        <v>13.35158288202788</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.2905782265316657</v>
+        <v>0.6214390799489438</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.341949402108933</v>
+        <v>-1.7994939967812</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>2408</v>
+        <v>2369</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>菱生</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>425.0667721724499</v>
+        <v>424.3920778015262</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>503</v>
+        <v>31.25</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>50.98652261854292</v>
+        <v>50.39573472492294</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>13.35158288202788</v>
+        <v>16.88014087372637</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.6214390799489438</v>
+        <v>0.5273223571435459</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-1.7994939967812</v>
+        <v>0.2967965957789135</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>2369</v>
+        <v>2352</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>菱生</t>
+          <t>佳世達</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>424.3920778015262</v>
+        <v>424.2262204859846</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>31.25</v>
+        <v>29</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>50.39573472492294</v>
+        <v>50.65241521578172</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>16.88014087372637</v>
+        <v>18.77315284939832</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.5273223571435459</v>
+        <v>0.4997094857052206</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.2967965957789135</v>
+        <v>0.0625257244008772</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5721,21 +5721,21 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>2352</v>
+        <v>2405</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>佳世達</t>
+          <t>輔信</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>424.2262204859846</v>
+        <v>424.088159320306</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>29</v>
+        <v>15.05</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>50.65241521578172</v>
+        <v>45.53810146645605</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>18.77315284939832</v>
+        <v>20.87364037095257</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.4997094857052206</v>
+        <v>0.7443935630658249</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.0625257244008772</v>
+        <v>0.0689249247390242</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>2405</v>
+        <v>1785</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>輔信</t>
+          <t>光洋科</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>424.088159320306</v>
+        <v>418.0836760282951</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>15.05</v>
+        <v>95.8</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>45.53810146645605</v>
+        <v>39.33347979389713</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>20.87364037095257</v>
+        <v>26.8883656200478</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.7443935630658249</v>
+        <v>0.7104465843872415</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,11 +5817,11 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0689249247390242</v>
+        <v>0.3327942130494321</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
